--- a/data/trans_camb/P1404-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1404-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,54</t>
+          <t>7,33</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>4,75</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,49</t>
+          <t>6,09</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 9,39</t>
+          <t>0,19; 9,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 12,7</t>
+          <t>3,12; 12,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 11,61</t>
+          <t>2,94; 11,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 7,98</t>
+          <t>-2,55; 8,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 9,96</t>
+          <t>-1,94; 9,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 10,25</t>
+          <t>-0,26; 9,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 7,28</t>
+          <t>-0,26; 7,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 9,31</t>
+          <t>2,21; 9,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 9,65</t>
+          <t>2,66; 9,24</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>143,4%</t>
+          <t>139,44%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>81,61%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 252,83</t>
+          <t>-2,18; 267,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,56; 345,8</t>
+          <t>37,01; 334,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,7; 354,03</t>
+          <t>31,13; 323,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,66; 115,19</t>
+          <t>-22,22; 126,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 139,91</t>
+          <t>-17,8; 130,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 149,02</t>
+          <t>-2,66; 129,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 116,27</t>
+          <t>-3,84; 120,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,62; 147,39</t>
+          <t>23,56; 157,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,99; 168,91</t>
+          <t>27,06; 159,41</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,72</t>
+          <t>4,24</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>3,52</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 10,09</t>
+          <t>1,94; 9,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 7,48</t>
+          <t>0,18; 7,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 7,2</t>
+          <t>0,31; 8,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 9,78</t>
+          <t>1,22; 9,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 8,12</t>
+          <t>-0,53; 8,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 6,81</t>
+          <t>-0,88; 6,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 8,39</t>
+          <t>2,69; 8,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,81</t>
+          <t>1,29; 6,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 5,78</t>
+          <t>0,63; 5,78</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,75; 157,86</t>
+          <t>18,7; 162,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 134,31</t>
+          <t>2,52; 132,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 120,76</t>
+          <t>1,67; 145,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,73; 118,55</t>
+          <t>9,83; 119,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 94,63</t>
+          <t>-5,05; 100,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 85,6</t>
+          <t>-7,68; 75,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,3; 111,43</t>
+          <t>25,4; 110,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,14; 87,77</t>
+          <t>13,71; 88,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 75,66</t>
+          <t>5,89; 75,57</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>6,53</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,4</t>
+          <t>8,41</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,6</t>
+          <t>7,53</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 7,34</t>
+          <t>-1,74; 7,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 9,21</t>
+          <t>-0,07; 9,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 11,29</t>
+          <t>1,95; 11,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 9,77</t>
+          <t>0,09; 9,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 11,76</t>
+          <t>1,18; 11,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,06; 12,44</t>
+          <t>3,9; 12,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,02</t>
+          <t>0,69; 7,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 8,94</t>
+          <t>2,22; 9,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 10,28</t>
+          <t>4,09; 10,51</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>101,24%</t>
+          <t>101,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,23; 120,73</t>
+          <t>-18,53; 116,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 158,2</t>
+          <t>-2,02; 150,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,83; 183,87</t>
+          <t>15,59; 181,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 155,71</t>
+          <t>-1,42; 161,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,08; 181,41</t>
+          <t>9,98; 182,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,7; 204,22</t>
+          <t>34,02; 215,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,2; 106,57</t>
+          <t>5,24; 103,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,33; 137,25</t>
+          <t>23,36; 137,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41,83; 156,83</t>
+          <t>41,37; 156,84</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9,56</t>
+          <t>9,02</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,24</t>
+          <t>10,02</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,11</t>
+          <t>9,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 9,88</t>
+          <t>0,91; 10,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 10,73</t>
+          <t>1,76; 10,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,8; 14,92</t>
+          <t>4,3; 14,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,46; 13,93</t>
+          <t>6,08; 14,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,43; 13,59</t>
+          <t>4,27; 13,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,12</t>
+          <t>6,15; 13,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,69; 10,83</t>
+          <t>4,77; 10,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,85; 10,01</t>
+          <t>4,42; 10,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,46; 11,47</t>
+          <t>6,65; 12,37</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>145,92%</t>
+          <t>137,66%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>120,85%</t>
+          <t>167,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>129,38%</t>
+          <t>152,21%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,09; 202,8</t>
+          <t>5,87; 197,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,45; 232,9</t>
+          <t>19,04; 222,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54,89; 300,64</t>
+          <t>48,68; 282,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66,03; 329,69</t>
+          <t>69,31; 313,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>52,23; 298,53</t>
+          <t>49,25; 291,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,8; 269,3</t>
+          <t>76,09; 321,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,91; 206,3</t>
+          <t>58,5; 209,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>52,97; 195,37</t>
+          <t>55,61; 207,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>54,07; 225,73</t>
+          <t>83,79; 247,19</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9,5</t>
+          <t>8,07</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,49</t>
+          <t>14,6</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12,68</t>
+          <t>11,47</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 11,92</t>
+          <t>-2,02; 11,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 7,71</t>
+          <t>-4,31; 7,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,1; 16,22</t>
+          <t>1,51; 14,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,45; 19,24</t>
+          <t>4,79; 18,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 10,52</t>
+          <t>-1,7; 11,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,26; 20,95</t>
+          <t>8,15; 20,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,04; 13,29</t>
+          <t>3,58; 13,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 7,87</t>
+          <t>-1,15; 7,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,64; 17,14</t>
+          <t>6,92; 15,25</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>151,04%</t>
+          <t>142,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>117,76%</t>
+          <t>106,46%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 145,28</t>
+          <t>-15,26; 140,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-33,48; 93,59</t>
+          <t>-32,13; 97,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19,92; 217,03</t>
+          <t>8,75; 181,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27,24; 273,71</t>
+          <t>33,54; 249,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 159,59</t>
+          <t>-14,55; 154,87</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,66; 296,4</t>
+          <t>52,84; 305,2</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,23; 148,59</t>
+          <t>26,8; 156,67</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 91,62</t>
+          <t>-9,14; 94,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>62,69; 208,07</t>
+          <t>48,77; 177,44</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15,05</t>
+          <t>14,59</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,25</t>
+          <t>4,22</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9,64</t>
+          <t>9,37</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,18; 13,47</t>
+          <t>3,67; 13,28</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,44; 9,61</t>
+          <t>0,49; 9,49</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10,62; 20,03</t>
+          <t>9,8; 19,33</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 7,89</t>
+          <t>-4,15; 7,95</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 2,41</t>
+          <t>-8,57; 2,95</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 8,96</t>
+          <t>-1,13; 9,23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,06</t>
+          <t>1,54; 9,29</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 4,45</t>
+          <t>-2,35; 4,93</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,88; 13,2</t>
+          <t>6,11; 12,81</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>262,69%</t>
+          <t>254,66%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>100,09%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>38,85; 353,2</t>
+          <t>42,06; 331,45</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0,75; 239,69</t>
+          <t>2,15; 243,49</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>126,78; 532,85</t>
+          <t>117,44; 497,61</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 75,98</t>
+          <t>-27,15; 73,65</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-52,19; 25,0</t>
+          <t>-51,45; 27,97</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 87,76</t>
+          <t>-7,0; 90,13</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,15; 116,68</t>
+          <t>12,66; 116,06</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-24,93; 56,25</t>
+          <t>-22,23; 61,74</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>50,15; 172,12</t>
+          <t>50,6; 159,97</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9,48</t>
+          <t>10,16</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,22</t>
+          <t>7,47</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>20,04</t>
+          <t>8,81</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,13</t>
+          <t>1,66; 8,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,27; 7,98</t>
+          <t>1,32; 7,58</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,67; 12,83</t>
+          <t>6,6; 13,68</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 4,17</t>
+          <t>-3,15; 4,08</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 2,95</t>
+          <t>-4,04; 3,14</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,48; 63,89</t>
+          <t>4,1; 11,04</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,2; 4,99</t>
+          <t>0,16; 4,86</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,56</t>
+          <t>-0,28; 4,65</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7,74; 49,83</t>
+          <t>6,28; 11,16</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>146,33%</t>
+          <t>156,89%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>248,22%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>228,65%</t>
+          <t>100,5%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>18,07; 156,44</t>
+          <t>17,09; 157,39</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>15,24; 153,41</t>
+          <t>17,01; 153,1</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>72,37; 261,02</t>
+          <t>80,9; 258,15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-24,6; 46,16</t>
+          <t>-24,73; 43,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-30,47; 30,84</t>
+          <t>-31,69; 33,06</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>54,04; 616,37</t>
+          <t>29,82; 125,17</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,14; 67,16</t>
+          <t>1,87; 63,25</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 59,79</t>
+          <t>-3,35; 61,24</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>81,2; 742,54</t>
+          <t>63,82; 149,64</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,45</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,38</t>
+          <t>1,61</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>0,82</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 0,89</t>
+          <t>-5,67; 0,77</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,65</t>
+          <t>-3,87; 2,45</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 1,56</t>
+          <t>-2,84; 3,16</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 2,86</t>
+          <t>-3,47; 2,97</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 6,0</t>
+          <t>-1,25; 5,61</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 5,93</t>
+          <t>-1,49; 4,59</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,86</t>
+          <t>-3,44; 1,11</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,36</t>
+          <t>-1,48; 3,16</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 2,26</t>
+          <t>-1,28; 3,07</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-22,75%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-3,81%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-42,88; 9,89</t>
+          <t>-46,36; 8,54</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-29,96; 29,32</t>
+          <t>-31,91; 27,41</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-65,74; 15,85</t>
+          <t>-23,19; 36,24</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 28,82</t>
+          <t>-26,13; 29,17</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 57,35</t>
+          <t>-9,78; 53,93</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 57,57</t>
+          <t>-11,39; 45,7</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-27,74; 8,7</t>
+          <t>-27,18; 11,71</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 33,17</t>
+          <t>-11,81; 29,84</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-43,35; 20,56</t>
+          <t>-10,21; 30,67</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>6,45</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,4</t>
+          <t>5,79</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>8,05</t>
+          <t>6,12</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,85</t>
+          <t>2,04; 5,01</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,04</t>
+          <t>2,19; 4,87</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,13</t>
+          <t>5,05; 7,9</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,15</t>
+          <t>1,79; 5,05</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,49</t>
+          <t>1,24; 4,53</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,26; 25,02</t>
+          <t>4,35; 7,32</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,56</t>
+          <t>2,4; 4,41</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,31</t>
+          <t>2,17; 4,32</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5,09; 17,18</t>
+          <t>5,15; 7,19</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>100,95%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>21,72; 66,84</t>
+          <t>23,92; 68,49</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>25,63; 68,73</t>
+          <t>25,25; 67,66</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>33,69; 97,01</t>
+          <t>58,08; 108,56</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>16,7; 54,43</t>
+          <t>16,46; 52,22</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>11,85; 46,84</t>
+          <t>11,17; 47,24</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>50,02; 252,33</t>
+          <t>39,41; 79,08</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>25,36; 52,46</t>
+          <t>24,84; 50,87</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>22,61; 50,27</t>
+          <t>22,37; 49,36</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>54,87; 186,31</t>
+          <t>53,01; 83,48</t>
         </is>
       </c>
     </row>
